--- a/approval_forms/049_equipment_lifecycle_extension_request_form--approval_forms.xlsx
+++ b/approval_forms/049_equipment_lifecycle_extension_request_form--approval_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Asset Details</t>
+          <t>1. Asset Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Asset Type</t>
+          <t>2. Asset Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>3. Category</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Request Date</t>
+          <t>4. Request Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Supervisor Approval</t>
+          <t>5. Supervisor Approval</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Supervisor Name</t>
+          <t>6. Supervisor Name</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>7. Reason</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>8. Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Extension Request</t>
+          <t>9. Extension Request</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Asset Condition</t>
+          <t>10. Asset Condition</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>11. Location</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>12. Status</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Asset Serial No</t>
+          <t>13. Asset Serial No</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Request Date 2</t>
+          <t>14. Request Date 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Approval Status</t>
+          <t>15. Approval Status</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Supervisor E-Mail</t>
+          <t>16. Supervisor E-Mail</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Supervisor Phone</t>
+          <t>17. Supervisor Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,241 +916,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Supervisor Name</t>
+          <t>18. Supervisor Name</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>asset_status_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>asset_serial_no_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Serial No</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>request_date_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Request Date 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>approval_status_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Approval Status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>supervisor_email_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Supervisor E-Mail</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>supervisor_phone_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Supervisor Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>supervisor_name_3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Supervisor Name</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>asset_type_2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>category_2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1167,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1200,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -1217,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vehicle</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vehicle</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1234,29 +1004,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>machinery</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Operational</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>asset_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>operational</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1302,29 +1072,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Operational</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>extension_request_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1336,46 +1106,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>asset_condition_choices</t>
+          <t>extension_request_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>asset_condition_choices</t>
+          <t>extension_request_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1404,46 +1174,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>asset_location_choices</t>
+          <t>asset_condition_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>asset_location_choices</t>
+          <t>asset_condition_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Site</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1472,46 +1242,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>site</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Site</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>asset_status_choices</t>
+          <t>asset_location_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>field</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Field</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>asset_status_choices</t>
+          <t>asset_location_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1540,46 +1310,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>approval_status_choices</t>
+          <t>asset_status_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>approval_status_choices</t>
+          <t>asset_status_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denied</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1608,284 +1378,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>withdrawn</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>asset_status_2_choices</t>
+          <t>approval_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>asset_status_2_choices</t>
+          <t>approval_status_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>withdrawn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>asset_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>asset_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>approval_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>approval_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>approval_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Denied</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>approval_status_2_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>withdrawn</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>Withdrawn</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>asset_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Construction</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>asset_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>maintenance</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>asset_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>asset_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Construction</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>maintenance</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>operational</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>category_2_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
